--- a/output/full_scan/batch_seq1_2026-10-19.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-19.xlsx
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>224.6175339338074</v>
+        <v>224.6175339338073</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>11.6</v>

--- a/output/full_scan/batch_seq1_2026-10-19.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-19.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>996.5471786989845</v>
+        <v>1166.547178698984</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>26.4</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.93516432290046</v>
+        <v>68.93516439871922</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16.89342409584587</v>
+        <v>16.89342413194721</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>6.53981732885463</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,51 +570,51 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0446313435821041</v>
+        <v>0.0446313435700852</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1516</v>
+        <v>1103</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>854</v>
+        <v>1103.462381955831</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.55</v>
+        <v>13.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>72.81261401471747</v>
+        <v>60.95454217688361</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16.81551474120773</v>
+        <v>34.73148109873287</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.434070040980664</v>
+        <v>1.946238195583066</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.5360087807489256</v>
+        <v>0.0285341079086384</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1103</v>
+        <v>1303</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>823.4623819558307</v>
+        <v>1038.869339602259</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13.4</v>
+        <v>303.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.95454212469232</v>
+        <v>60.32286968440633</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.73148100668907</v>
+        <v>45.09480126969155</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.946238195583066</v>
+        <v>1.119784418897005</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0285341079206558</v>
+        <v>1.675126437400735</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1457</v>
+        <v>1216</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>811.4617180180261</v>
+        <v>997.3130029747276</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.81508324232039</v>
+        <v>71.0576512445512</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.7746300910653</v>
+        <v>24.31960719883312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.197955898738476</v>
+        <v>1.331300297472749</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0285054531413391</v>
+        <v>0.6899492362623192</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1512</v>
+        <v>1457</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>729.0440378064986</v>
+        <v>981.461718018026</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.46</v>
+        <v>14.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.46677792231441</v>
+        <v>60.81508324232039</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.8443957099228</v>
+        <v>14.77463012527342</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.928887090376579</v>
+        <v>2.197955898738476</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0282156201301635</v>
+        <v>0.0285054531413391</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1310</v>
+        <v>1476</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>696.9584050945048</v>
+        <v>899.5896201739392</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>321</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.83225283648426</v>
+        <v>65.17017602229532</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>47.67929599149603</v>
+        <v>39.01055173151416</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6372977393855699</v>
+        <v>0.5634395300385417</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.039907893529155</v>
+        <v>5.87470050749058</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1452</v>
+        <v>1512</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>684.1010054917849</v>
+        <v>899.0440378064987</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11.15</v>
+        <v>6.46</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.28737510578343</v>
+        <v>62.46677808038593</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.96071090273195</v>
+        <v>18.84439578115638</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.103711154000658</v>
+        <v>4.928887090376579</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0446920312361582</v>
+        <v>0.0282156201181459</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1563</v>
+        <v>1326</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>681.9461488073208</v>
+        <v>884.0287116912252</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81</v>
+        <v>75.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.89136489276022</v>
+        <v>54.74885433355568</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44.10186353638378</v>
+        <v>36.57512000502935</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6734771407117776</v>
+        <v>0.798973000883336</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0295413571916842</v>
+        <v>0.3638081999112392</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1303</v>
+        <v>1440</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>678.8652311678877</v>
+        <v>877.5894393943719</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>303.5</v>
+        <v>14.05</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.32286969032253</v>
+        <v>55.47838362531304</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45.09480128852685</v>
+        <v>23.20552425343566</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.119213259183187</v>
+        <v>0.5352067674073556</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.675126436956102</v>
+        <v>0.054929095053798</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1312</v>
+        <v>1102</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>674.5219224447446</v>
+        <v>876.0075082805597</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15.2</v>
+        <v>37.75</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>49.55278204144994</v>
+        <v>69.40619000187601</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>47.28435480632923</v>
+        <v>33.38340370948445</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8885231674751728</v>
+        <v>0.900824313423334</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0431616493658243</v>
+        <v>0.2061687514155448</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>671.4194757414463</v>
+        <v>866.9584050945048</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>78.2</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.54881042893376</v>
+        <v>56.8322528636323</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>40.92170241413452</v>
+        <v>47.67929600424189</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.779350243875352</v>
+        <v>0.6372977393855699</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8873564322216572</v>
+        <v>0.039907893483488</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>661.6867019863669</v>
+        <v>863.8554939882423</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12.8</v>
+        <v>71.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.39527278454919</v>
+        <v>59.11874753350974</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.83659508615202</v>
+        <v>54.05317836778053</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6676927672040681</v>
+        <v>0.6660209206742187</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.029940888069492</v>
+        <v>0.1589775212982087</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1101</v>
+        <v>1452</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>659.9684899321027</v>
+        <v>854.1010054917849</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27.15</v>
+        <v>11.15</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.54910139438062</v>
+        <v>59.28737533264184</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>48.31637624837807</v>
+        <v>14.96071086669754</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6023111016748984</v>
+        <v>5.103711154000658</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,48 +1206,48 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1679333979374698</v>
+        <v>0.0446920312361582</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1434</v>
+        <v>1516</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>655.1725482868187</v>
+        <v>854</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>19.9</v>
+        <v>18.55</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.92668543030878</v>
+        <v>72.81261402280258</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>38.95692282007888</v>
+        <v>16.81551481074131</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6172548286818703</v>
+        <v>5.434070040980664</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.1951993585378715</v>
+        <v>0.536008780733787</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1216</v>
+        <v>1313</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>642.3130029747275</v>
+        <v>831.6867019863669</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>71.05765101462755</v>
+        <v>55.39527284729466</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.31960702789906</v>
+        <v>34.83659526187414</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.331300297472749</v>
+        <v>0.6676927672040681</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.6899492366228467</v>
+        <v>0.0299408879853704</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1102</v>
+        <v>1477</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>631.0075082805597</v>
+        <v>828.0987202384376</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>37.75</v>
+        <v>207.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.40618988714606</v>
+        <v>61.80555724004963</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>33.38340366570556</v>
+        <v>31.66542268858188</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.900824313423334</v>
+        <v>0.6216826369922945</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2061687515597472</v>
+        <v>1.833810570405989</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1326</v>
+        <v>1434</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>629.0287116912253</v>
+        <v>825.1725482868187</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>75.5</v>
+        <v>19.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.74885431913243</v>
+        <v>62.92668546605415</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.57512007164352</v>
+        <v>38.95692283859124</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.798973000883336</v>
+        <v>0.6172548286818703</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3638082000314</v>
+        <v>0.195199358501818</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1440</v>
+        <v>1101</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>627.5894393943719</v>
+        <v>819.9684899321027</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14.05</v>
+        <v>27.15</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,29 +1453,29 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.47838364179381</v>
+        <v>63.54910141269284</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.2055243078427</v>
+        <v>48.31637626487306</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5352067674073556</v>
+        <v>0.6023111016748984</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0549290950778312</v>
+        <v>0.1679333978894009</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>619.1656820127455</v>
+        <v>819.1656820127455</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>79.09999999999999</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>72.50683092433528</v>
+        <v>72.50683097201961</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>68.18364567660595</v>
@@ -1524,11 +1524,11 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.7206739718718804</v>
+        <v>0.7206739716795969</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>619.1178965892526</v>
+        <v>819.1178965892526</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>16.5</v>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>66.47624583202415</v>
+        <v>66.47624592431747</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>16.4464381832925</v>
+        <v>16.44643820050425</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>8.657849759808846</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1674412517429026</v>
+        <v>0.1674412516828151</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1416</v>
+        <v>1301</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>618.9616184324302</v>
+        <v>786.4194757414463</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13.15</v>
+        <v>78.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>79.52626539066316</v>
+        <v>59.5488103916588</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>38.43394348956716</v>
+        <v>40.92170242209068</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9871331802361216</v>
+        <v>0.779350243875352</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.162025949676524</v>
+        <v>0.8873564324019165</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1315</v>
+        <v>1528</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>613.8554939882423</v>
+        <v>783.5835644272145</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>71.5</v>
+        <v>24.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.11874748486637</v>
+        <v>57.33893243266736</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>54.05317833137968</v>
+        <v>32.85958139915797</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6660209206742187</v>
+        <v>1.104568022144544</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1589775213462774</v>
+        <v>-0.2007023313252751</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1558</v>
+        <v>1416</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>606.8557500603889</v>
+        <v>778.9616184324301</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>115</v>
+        <v>13.15</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.45361625529478</v>
+        <v>79.52626539066316</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.71872920105197</v>
+        <v>38.43394374746532</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6299195579107392</v>
+        <v>0.9871331802361216</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1415708430786417</v>
+        <v>0.1620259496885416</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1528</v>
+        <v>1558</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>583.5835644272145</v>
+        <v>776.8557500603889</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>24.9</v>
+        <v>115</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.33893239440308</v>
+        <v>62.45361630842559</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.85958139033367</v>
+        <v>26.71872937455212</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.104568022144544</v>
+        <v>0.6299195579107392</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.2007023312411545</v>
+        <v>0.1415708428863578</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1323</v>
+        <v>1456</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>580.2827578178423</v>
+        <v>765.8343757512033</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21.85</v>
+        <v>14.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.826891247428</v>
+        <v>51.78579121147941</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25.53997359418378</v>
+        <v>25.01250664282238</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1870509255357995</v>
+        <v>0.3389641560902784</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,11 +1842,11 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0347476687205659</v>
+        <v>0.0210260732026826</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>572.8225616891268</v>
+        <v>762.8225616891268</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>28.85</v>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.12730741190033</v>
+        <v>54.12730748242197</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.82126917748541</v>
+        <v>20.82126935231607</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.7234424497556087</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1238930337268109</v>
+        <v>0.1238930336066423</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>561.1620363346891</v>
+        <v>750.2827578178423</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>81.5</v>
+        <v>21.85</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.95889841757407</v>
+        <v>58.8268912895986</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.51876087184272</v>
+        <v>25.53997347613687</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7017282799347442</v>
+        <v>0.1870509255357995</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4188461890803652</v>
+        <v>0.034747668708548</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1560</v>
+        <v>1321</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>559.7999269663965</v>
+        <v>742.3217616544841</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>867</v>
+        <v>35.85</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>44.53565642093393</v>
+        <v>79.69629573628268</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>39.02840405160698</v>
+        <v>25.06577782433276</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5989910313201274</v>
+        <v>0.8321761654484151</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-23.38452946520254</v>
+        <v>0.4129874710457101</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1477</v>
+        <v>1229</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>548.0987202384376</v>
+        <v>730.0960365701844</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>207.5</v>
+        <v>40.65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.80555725798236</v>
+        <v>50.69045447998477</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>31.66542266552852</v>
+        <v>20.73295818628855</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6216826369922945</v>
+        <v>0.7345820274809054</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.833810570886692</v>
+        <v>0.1759965201581906</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1321</v>
+        <v>1439</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>542.3217616544841</v>
+        <v>729.000393222852</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>35.85</v>
+        <v>29.15</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>79.69629579643077</v>
+        <v>52.26528179326996</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.06577789099329</v>
+        <v>15.95281829145591</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8321761654484151</v>
+        <v>0.8017068425692313</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4129874710937799</v>
+        <v>0.4820312893972073</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1409</v>
+        <v>1470</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>538.3539450998219</v>
+        <v>723.0179079225909</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.96104593237949</v>
+        <v>51.99235976648061</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>25.40222581505822</v>
+        <v>13.4515372967766</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5432560883721093</v>
+        <v>1.443410022942113</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0407531084551344</v>
+        <v>-0.911108235602626</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1476</v>
+        <v>1409</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>524.5896201739392</v>
+        <v>708.3539450998219</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>321</v>
+        <v>25.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.17017577673727</v>
+        <v>51.96104600456339</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>39.01055175225051</v>
+        <v>25.4022260237971</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5634395300385417</v>
+        <v>0.5432560883721093</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>5.874700510014185</v>
+        <v>0.0407531082748754</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1456</v>
+        <v>1514</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>515.8343757512033</v>
+        <v>703.9507302093712</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>14.8</v>
+        <v>99.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.78579115399379</v>
+        <v>42.88865990558148</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.0125065793029</v>
+        <v>13.35071533929678</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3389641560902784</v>
+        <v>0.9452311547421944</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0210260732147007</v>
+        <v>-0.2474293778861379</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1418</v>
+        <v>1319</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>497.8756465390305</v>
+        <v>701.1620363346891</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.4</v>
+        <v>81.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.69490645009481</v>
+        <v>54.95889846705099</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>41.0967170418567</v>
+        <v>26.51876087635773</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4825363194170806</v>
+        <v>0.7017282799347442</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0142856000726004</v>
+        <v>0.4188461891765072</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1325</v>
+        <v>1563</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>485.4524192635333</v>
+        <v>681.9461488073208</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>27.55</v>
+        <v>81</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.57431118587307</v>
+        <v>56.89136492554555</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>33.61349431159495</v>
+        <v>44.10186353638379</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4855864129102302</v>
+        <v>0.6734771407117776</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1056875221605236</v>
+        <v>0.0295413571505096</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1524</v>
+        <v>1504</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>477.8905793939006</v>
+        <v>677.0283082406555</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>27.05</v>
+        <v>69.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.49201883504877</v>
+        <v>46.73988619082538</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>31.496381664168</v>
+        <v>15.90618031141286</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8890579393900568</v>
+        <v>0.8352807961739586</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1719460796368848</v>
+        <v>-0.0796751660532975</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1514</v>
+        <v>1560</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>473.9507302093782</v>
+        <v>674.7999269663965</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>99.8</v>
+        <v>867</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>42.88865990558148</v>
+        <v>44.53565644072989</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.35071525746787</v>
+        <v>39.0284040818761</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9452311547421944</v>
+        <v>0.5989910313201274</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.2474293780062969</v>
+        <v>-23.38452946508231</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1304</v>
+        <v>1445</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>472.5087464997131</v>
+        <v>670.9946481788668</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>13.15</v>
+        <v>10.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.95081684398223</v>
+        <v>47.22161155989451</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>39.18512461433083</v>
+        <v>28.44432732831964</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5769989134980513</v>
+        <v>0.3636964607990863</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0561805939219955</v>
+        <v>0.0060596816967696</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1455</v>
+        <v>1418</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>470.8795726705331</v>
+        <v>667.8756465390305</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.84196369582258</v>
+        <v>53.69490683618704</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>36.21293979806988</v>
+        <v>41.09671731148248</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.300181735201753</v>
+        <v>0.4825363194170806</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0068130309671491</v>
+        <v>-0.0142856002768969</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>465.6038586465583</v>
+        <v>664.5219224447446</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>8.82</v>
+        <v>15.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.57402241010816</v>
+        <v>49.55278207084636</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>39.65517510829086</v>
+        <v>47.28435493093667</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3186256097540481</v>
+        <v>0.8885231674751728</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0296043918885901</v>
+        <v>0.0431616492817023</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1513</v>
+        <v>1304</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>462.3181062478016</v>
+        <v>662.5087464997123</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>162</v>
+        <v>13.15</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>41.43996659801546</v>
+        <v>54.95081686966626</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9.756643338830422</v>
+        <v>39.18512462026776</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.119761936807773</v>
+        <v>0.5769989134980513</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.4880323586207866</v>
+        <v>0.0561805938619102</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1305</v>
+        <v>1210</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>450.2381307905216</v>
+        <v>661.0811324750275</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>12.85</v>
+        <v>51.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.24703367760736</v>
+        <v>42.11908924254054</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>32.91146965580845</v>
+        <v>24.2447820314107</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6503465683647117</v>
+        <v>0.9946351903428224</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0538026389022122</v>
+        <v>0.0519591134864036</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1439</v>
+        <v>1524</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>449.000393222852</v>
+        <v>647.8905793939006</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>29.15</v>
+        <v>27.05</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.26528178808339</v>
+        <v>57.49201899227213</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15.95281829214799</v>
+        <v>31.49638166949543</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8017068425692313</v>
+        <v>0.8890579393900568</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.4820312893731721</v>
+        <v>0.1719460796609209</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1504</v>
+        <v>1513</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>447.0283082406548</v>
+        <v>642.3181062478016</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.3</v>
+        <v>162</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.73988586630646</v>
+        <v>41.43996659801546</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.90618029725634</v>
+        <v>9.75664333817077</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8352807961739586</v>
+        <v>1.119761936807773</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0796751649717176</v>
+        <v>-0.4880323585006073</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1441</v>
+        <v>1463</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>445.7987260277681</v>
+        <v>639.9462855719969</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>9.74</v>
+        <v>18</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>60.72263068403012</v>
+        <v>64.0638104692492</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.78013222015434</v>
+        <v>16.320507341777</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1568585936807803</v>
+        <v>0.6901650767786824</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0064773371903498</v>
+        <v>0.0507460189921216</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1470</v>
+        <v>1441</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>443.017907922591</v>
+        <v>635.7987260277685</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>24.5</v>
+        <v>9.74</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.99236005980894</v>
+        <v>60.72263053289991</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.45153830113315</v>
+        <v>26.78013222015434</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.443410022942113</v>
+        <v>0.1568585936807803</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.9111082404215624</v>
+        <v>-0.0064773372094201</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1308</v>
+        <v>1220</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>429.2414246930604</v>
+        <v>630.3551492354514</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>14.35</v>
+        <v>10.95</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.91813149093809</v>
+        <v>56.02077947319349</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>38.12463955455686</v>
+        <v>18.90364479398858</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.549496433644674</v>
+        <v>0.9872599676100872</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0039922031311627</v>
+        <v>0.014284377613645</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1443</v>
+        <v>1472</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>423.5608303405835</v>
+        <v>615.2495387130589</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>22.65</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.12023297425782</v>
+        <v>52.8871438134634</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.06310008978524</v>
+        <v>7.277965417196296</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4971343031766642</v>
+        <v>0.805790557453233</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0077213275728373</v>
+        <v>0.0284202429393736</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1309</v>
+        <v>1455</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>408.84735338743</v>
+        <v>610.879572670533</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>14.25</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.88617988459668</v>
+        <v>49.84196373493867</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>39.3706430672783</v>
+        <v>36.21293988991027</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5818137186345923</v>
+        <v>0.300181735201753</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0259363614784831</v>
+        <v>-0.0068130309935867</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1232</v>
+        <v>1305</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>399.6726839252135</v>
+        <v>610.2381307905217</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>155.5</v>
+        <v>12.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.34270594473997</v>
+        <v>54.24703370785594</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.76810564938825</v>
+        <v>32.91146968825795</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.329895776312838</v>
+        <v>0.6503465683647117</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.317406091344649</v>
+        <v>0.0538026388421267</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1256</v>
+        <v>1314</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>393.1384676171288</v>
+        <v>605.6038586465584</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>165.5</v>
+        <v>8.82</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>39.39189819763946</v>
+        <v>51.5740224285377</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9.407588909808039</v>
+        <v>39.65517517396318</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7362462471215787</v>
+        <v>0.3186256097540481</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3321120394318329</v>
+        <v>-0.0296043919150267</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1445</v>
+        <v>1309</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>390.9946481788668</v>
+        <v>598.84735338743</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.1</v>
+        <v>14.25</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.22161140191102</v>
+        <v>51.88617990526561</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.44432738264164</v>
+        <v>39.37064314378318</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3636964607990863</v>
+        <v>0.5818137186345923</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0060596816967696</v>
+        <v>0.0259363614304136</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1459</v>
+        <v>1474</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>377.8014943724034</v>
+        <v>586.3991724897402</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>18.1</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>59.95993963097286</v>
+        <v>47.80317047436286</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>65.04441009622802</v>
+        <v>13.97015144763674</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3274303556341761</v>
+        <v>0.3620295653546305</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0731804638300146</v>
+        <v>-0.0004542397760419</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1210</v>
+        <v>1413</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>376.0811324750276</v>
+        <v>576.9153628486828</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>51.3</v>
+        <v>9.42</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.11908902067144</v>
+        <v>54.95770563925988</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.24478201107429</v>
+        <v>9.384501101859129</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9946351903428224</v>
+        <v>0.0508192055941781</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0519591135585055</v>
+        <v>0.0272886029134232</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>375.9047677808711</v>
+        <v>571.0742920694387</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>24.55</v>
+        <v>28</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.50244704202176</v>
+        <v>47.34841778670526</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>29.19563064068877</v>
+        <v>12.45841938311486</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.462342790344954</v>
+        <v>1.266669521981381</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0889753160882619</v>
+        <v>0.0207637821244284</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1539</v>
+        <v>1232</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>366.5113311164252</v>
+        <v>569.6726839252134</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15.45</v>
+        <v>155.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>42.09132673532925</v>
+        <v>53.34270606679691</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>30.41483863588899</v>
+        <v>17.76810564938825</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.420887968258059</v>
+        <v>1.329895776312838</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0061988436969638</v>
+        <v>0.3174060912244774</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1229</v>
+        <v>1308</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>365.0960365701844</v>
+        <v>569.2414246930605</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>40.65</v>
+        <v>14.35</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.69045465908711</v>
+        <v>48.91813149093809</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.73295804172406</v>
+        <v>38.12463962699558</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7345820274809054</v>
+        <v>0.549496433644674</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1759965200019699</v>
+        <v>-0.0039922031792326</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1463</v>
+        <v>1443</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>359.9462855719967</v>
+        <v>563.5608303405835</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>18</v>
+        <v>22.65</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>64.06381070947785</v>
+        <v>44.12023287047586</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.32050740216848</v>
+        <v>13.06310008362404</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6901650767786824</v>
+        <v>0.4971343031766642</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0507460189320359</v>
+        <v>-0.0077213274766989</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1220</v>
+        <v>1459</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>350.3551492354514</v>
+        <v>547.8014943724033</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10.95</v>
+        <v>18.1</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>56.020779234213</v>
+        <v>59.95993970192849</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.90364478183228</v>
+        <v>65.04441033688674</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9872599676100872</v>
+        <v>0.3274303556341761</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0142843776496985</v>
+        <v>-0.0731804638917998</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1568</v>
+        <v>1225</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>350.1130268832524</v>
+        <v>545.904767780871</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>29.1</v>
+        <v>24.55</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.44270519688804</v>
+        <v>49.5024467259655</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.17709537922686</v>
+        <v>29.19563085493737</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9699421165124102</v>
+        <v>0.462342790344954</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.3119739975219272</v>
+        <v>0.0889753163165897</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1454</v>
+        <v>1256</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>342.0336709326746</v>
+        <v>533.1384676171289</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>12.6</v>
+        <v>165.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.61737050712036</v>
+        <v>39.3918981750202</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25.28709473633922</v>
+        <v>9.407588900533344</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.036776325956798</v>
+        <v>0.7362462471215787</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0470080614052757</v>
+        <v>0.3321120396721748</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1451</v>
+        <v>1503</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>340.1184184994553</v>
+        <v>511.8454286703729</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>17.1</v>
+        <v>194</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.51949957724533</v>
+        <v>43.85036527006033</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.79083347976184</v>
+        <v>11.0386779138973</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.097133167293731</v>
+        <v>1.026186174544157</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0208163113160939</v>
+        <v>0.032661707296498</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1472</v>
+        <v>1451</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>335.2495387130592</v>
+        <v>510.1184184994558</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.88714382519294</v>
+        <v>49.5194997545462</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7.27796543674897</v>
+        <v>14.79083355367714</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.805790557453233</v>
+        <v>1.097133167293731</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.028420242771133</v>
+        <v>0.0208163112920586</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>321.5923377943921</v>
+        <v>506.5113311164252</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>18.9</v>
+        <v>15.45</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>30.96794398961394</v>
+        <v>42.09132666037105</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>48.45191762058666</v>
+        <v>30.41483863588899</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.592230867738393</v>
+        <v>1.420887968258059</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0087527970182536</v>
+        <v>-0.0061988436969638</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1233</v>
+        <v>1325</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>321.0742920694386</v>
+        <v>505.4524192635334</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>28</v>
+        <v>27.55</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.34841783673872</v>
+        <v>51.57431121802512</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.45841941550911</v>
+        <v>33.61349437049716</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.266669521981381</v>
+        <v>0.4855864129102302</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,11 +3962,11 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0207637821003949</v>
+        <v>0.105687522112453</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>320.1419524464541</v>
+        <v>480.1419524464541</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>23.4</v>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>33.85983554054053</v>
+        <v>33.85983561901567</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7.335571316229284</v>
+        <v>7.335571360510445</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>1.624634159245956</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0287248185089029</v>
+        <v>-0.0287248185569709</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>317.5320547613664</v>
+        <v>478.1596864529293</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>37.84288628687305</v>
+        <v>51.82257067199687</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.4945209927032</v>
+        <v>7.716016009963573</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.813496925788564</v>
+        <v>0.7251461988304093</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0048745771823839</v>
+        <v>1.463406502638593</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1419</v>
+        <v>1464</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>312.3858378854779</v>
+        <v>472.570449215099</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>62.9</v>
+        <v>9.91</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>31.89259189835953</v>
+        <v>39.79177789149352</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.73107619698266</v>
+        <v>23.60460678461332</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.464325693686261</v>
+        <v>0.6141546670778475</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.2001943915241254</v>
+        <v>0.0073366327369832</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1444</v>
+        <v>1108</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>308.523873973382</v>
+        <v>467.0574406213608</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>6.85</v>
+        <v>11.05</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.28692050672466</v>
+        <v>35.57356666565728</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.12607058216741</v>
+        <v>36.98907360538826</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9863864999615108</v>
+        <v>1.380261820294185</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0118360730621084</v>
+        <v>0.0259739309569075</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>306.3991724897403</v>
+        <v>461.592337794392</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.80317041486552</v>
+        <v>30.96794472242053</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.9701515460843</v>
+        <v>48.45191765592647</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3620295653546305</v>
+        <v>0.592230867738393</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0004542397640237</v>
+        <v>-0.0087527970182536</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1519</v>
+        <v>1342</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>302.7134485326376</v>
+        <v>457.5320547613664</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>644</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>38.30781514567055</v>
+        <v>37.84288675717017</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.1835773147189</v>
+        <v>15.49452096593588</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7901326335294454</v>
+        <v>1.813496925788564</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-4.909331117570293</v>
+        <v>-0.0048745770862516</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1527</v>
+        <v>1444</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>299.4910896205442</v>
+        <v>448.523873973382</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>32.35</v>
+        <v>6.85</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.1430881749642</v>
+        <v>45.28692062992006</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9.072285850718874</v>
+        <v>24.1260706018174</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5606774886811253</v>
+        <v>0.9863864999615108</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0141474187592483</v>
+        <v>0.0118360730404774</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1413</v>
+        <v>1465</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>296.9153628486828</v>
+        <v>448.4792408744037</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>9.42</v>
+        <v>11.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.95770556594621</v>
+        <v>46.05729607928532</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9.384501109522892</v>
+        <v>19.81727637566512</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.0508192055941781</v>
+        <v>1.59767753347286</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0272886029254393</v>
+        <v>0.0436397240212806</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1339</v>
+        <v>1414</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>285.5434537615272</v>
+        <v>441.3573777114342</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>42</v>
+        <v>17.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>40.474160285342</v>
+        <v>51.78737607214119</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>27.30278457336172</v>
+        <v>19.00191765293444</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8046795763135517</v>
+        <v>0.9399002986829532</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0280269099128034</v>
+        <v>0.0855203027425384</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1467</v>
+        <v>1532</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>285.3723399915932</v>
+        <v>440.1793555867957</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8.02</v>
+        <v>21.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.74962249642964</v>
+        <v>40.9786742520131</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.38261226906026</v>
+        <v>21.87388517069697</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5476770365888757</v>
+        <v>0.6240940712414285</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0089077360522742</v>
+        <v>-0.007913297011926499</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1503</v>
+        <v>1522</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>281.8454286703729</v>
+        <v>439.8269159653194</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>194</v>
+        <v>26.85</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.85036516260995</v>
+        <v>52.59609949620742</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.0386779138973</v>
+        <v>15.1060249429473</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.026186174544157</v>
+        <v>0.5822511868523909</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0326617080175398</v>
+        <v>0.1744902072874714</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1324</v>
+        <v>1527</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>273.0733947847243</v>
+        <v>439.4910896205442</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>9.94</v>
+        <v>32.35</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.45095679959629</v>
+        <v>44.14308824885708</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.29261278690503</v>
+        <v>9.0722858613636</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1758318863399298</v>
+        <v>0.5606774886811253</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0023278613360417</v>
+        <v>-0.0141474187352166</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1414</v>
+        <v>1446</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>271.3573777114341</v>
+        <v>433.1209022280737</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>17.8</v>
+        <v>13.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.78737596393554</v>
+        <v>46.68895844239164</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.00191746691558</v>
+        <v>13.27500243283604</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9399002986829532</v>
+        <v>0.5468840712643926</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0855203028249218</v>
+        <v>0.0196980248936591</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1522</v>
+        <v>1535</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>269.8269159653193</v>
+        <v>429.4986529799841</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>26.85</v>
+        <v>45.95</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.59609943625904</v>
+        <v>53.93939462347832</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.10602498407525</v>
+        <v>19.76407770786324</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5822511868523909</v>
+        <v>0.6388612464137525</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1744902071913333</v>
+        <v>0.0593198321059621</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1535</v>
+        <v>1419</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>259.4986529799841</v>
+        <v>427.3858378854802</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>45.95</v>
+        <v>62.9</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>53.93939441403781</v>
+        <v>31.89259200421669</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.76407764053744</v>
+        <v>11.73107625186263</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6388612464137525</v>
+        <v>2.464325693686261</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0593198322261302</v>
+        <v>-0.2001943917644786</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1465</v>
+        <v>1339</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>258.4792408744037</v>
+        <v>425.5434537615273</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>11.7</v>
+        <v>42</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.05729611320702</v>
+        <v>40.47416032188869</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.81727631739684</v>
+        <v>27.30278457336172</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.59767753347286</v>
+        <v>0.8046795763135517</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0436397239972441</v>
+        <v>0.0280269100329766</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1338</v>
+        <v>1467</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>258.192349592736</v>
+        <v>425.3723399915932</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>14.45</v>
+        <v>8.02</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>41.25451354622844</v>
+        <v>44.74962253043331</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.65187821645037</v>
+        <v>17.38261241065173</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2698160318642114</v>
+        <v>0.5476770365888757</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0562082944148727</v>
+        <v>0.0089077360426595</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1515</v>
+        <v>1203</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>256.6020147913164</v>
+        <v>424.688745723298</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>28.35</v>
+        <v>43.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.02839055849042</v>
+        <v>48.09810657156458</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6.759030002594124</v>
+        <v>8.282499242890218</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.081651076388518</v>
+        <v>0.7134200073207435</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0861428082246531</v>
+        <v>0.0618276437578453</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1460</v>
+        <v>1324</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>255.7420508264363</v>
+        <v>413.073394784725</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6.12</v>
+        <v>9.94</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>34.86964514787013</v>
+        <v>46.45095708498149</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>27.61042784171197</v>
+        <v>20.29261274895617</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.211731307565881</v>
+        <v>0.1758318863399298</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.010852829469088</v>
+        <v>0.0023278613480611</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1436</v>
+        <v>1468</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>247.7585275784968</v>
+        <v>408.5325403139668</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>35.6</v>
+        <v>13.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.92426286521721</v>
+        <v>49.27045529187829</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.6282626251281</v>
+        <v>8.179543341605802</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7732755483416566</v>
+        <v>0.588154802343977</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0946968917348652</v>
+        <v>-0.0039522324008993</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1537</v>
+        <v>1453</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>247.5971594137286</v>
+        <v>407.1046875105091</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>114</v>
+        <v>10.95</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>40.78800791940163</v>
+        <v>49.04554301668595</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.1801968630377</v>
+        <v>18.57739113038998</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.128792565418971</v>
+        <v>1.028898222745037</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2988834517270133</v>
+        <v>0.0175551664630841</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1340</v>
+        <v>1466</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>246.4782910167605</v>
+        <v>407.0860655902181</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>5.05</v>
+        <v>14.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.79241097581907</v>
+        <v>48.1551992899625</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10.95323903081297</v>
+        <v>17.79244933363873</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6046818612906698</v>
+        <v>1.585509426776315</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0160106488850637</v>
+        <v>0.050921654999154</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1437</v>
+        <v>1338</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>245.6239892026434</v>
+        <v>398.1923495927359</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>30.85</v>
+        <v>14.45</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>32.88231719690405</v>
+        <v>41.25451356369918</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19.51522834512115</v>
+        <v>29.65187821645038</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4312676639729217</v>
+        <v>0.2698160318642114</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1154644979897278</v>
+        <v>-0.0562082944629416</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>244.0388938010439</v>
+        <v>396.6020147913164</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25.3</v>
+        <v>28.35</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.42713871238291</v>
+        <v>41.02839039979931</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.70986708188259</v>
+        <v>6.759030176073472</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4694328323589724</v>
+        <v>1.081651076388518</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0291479143827362</v>
+        <v>0.0861428084650004</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1538</v>
+        <v>1460</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>243.7148834084768</v>
+        <v>395.7420508264364</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.74514951904633</v>
+        <v>34.86964515870845</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.12221864706801</v>
+        <v>27.61042781204531</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.0130458585223235</v>
+        <v>1.211731307565881</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.6609080684849016</v>
+        <v>0.0108528294642804</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1447</v>
+        <v>1506</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>241.6144018708988</v>
+        <v>393.2009031902898</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>6.45</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.14850238312732</v>
+        <v>35.74750444701472</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>25.25226910431892</v>
+        <v>20.18153374921351</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.072867636151975</v>
+        <v>0.7106999952268025</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0134402701239656</v>
+        <v>0.0113642032957013</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>237.6321817322164</v>
+        <v>390.2110089135179</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>10.4</v>
+        <v>31.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.98283329740866</v>
+        <v>50.46239673355453</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.24815117160554</v>
+        <v>12.00480239221263</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7526695038869646</v>
+        <v>1.128383580968058</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0027043735740916</v>
+        <v>0.0215521687075583</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1453</v>
+        <v>1436</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>237.104687510509</v>
+        <v>387.7585275784968</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>10.95</v>
+        <v>35.6</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.04554288704951</v>
+        <v>39.92426279937508</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.57739100541681</v>
+        <v>11.6282625896706</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.028898222745037</v>
+        <v>0.7732755483416566</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0175551664871193</v>
+        <v>0.0946968916627642</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1466</v>
+        <v>1537</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>237.0860655902181</v>
+        <v>387.5971594137287</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14.7</v>
+        <v>114</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.15519927263887</v>
+        <v>40.78800810575732</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.79244929115757</v>
+        <v>23.18019682684501</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.585509426776315</v>
+        <v>1.128792565418971</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.050921654999154</v>
+        <v>0.2988834514866645</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1231</v>
+        <v>1340</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>235.3938416419151</v>
+        <v>386.4782910167583</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>76</v>
+        <v>5.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>26.94807887687968</v>
+        <v>40.79241104521838</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>28.19883453023129</v>
+        <v>10.95323915187624</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.246451296204247</v>
+        <v>0.6046818612906698</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1689448333302734</v>
+        <v>-0.0160106489042913</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1530</v>
+        <v>1437</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>233.4498503776814</v>
+        <v>385.6239892026434</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.55</v>
+        <v>30.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>42.86116932517829</v>
+        <v>32.88231711981044</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.69120798483803</v>
+        <v>19.51522842973641</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5864870653200853</v>
+        <v>0.4312676639729217</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.07035506696368531</v>
+        <v>-0.1154644980017463</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1506</v>
+        <v>1521</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>233.2009031902897</v>
+        <v>384.038893801044</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>35.74750663885935</v>
+        <v>44.42713871238291</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.18153224399429</v>
+        <v>26.70986703290655</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7106999952268025</v>
+        <v>0.4694328323589724</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0113642029952689</v>
+        <v>-0.0291479143707197</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1442</v>
+        <v>1541</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>231.2527330883118</v>
+        <v>383.4909676852952</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26.5</v>
+        <v>20.35</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.95069668413525</v>
+        <v>51.09945415237968</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>30.51690297595155</v>
+        <v>11.75884351504856</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2990637034167111</v>
+        <v>2.466753917329334</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0188999135468945</v>
+        <v>0.1663491580379266</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1109</v>
+        <v>1525</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>230.452268160796</v>
+        <v>383.1905600840465</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>13.05</v>
+        <v>62.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>34.10517812479573</v>
+        <v>50.35016855156348</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>37.64021498518915</v>
+        <v>9.26565333183513</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.030622623823407</v>
+        <v>0.5403780714278046</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.008447590068498999</v>
+        <v>0.367921628049492</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1307</v>
+        <v>1227</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>230.2110089135179</v>
+        <v>382.9938240747165</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>31.1</v>
+        <v>28.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>50.46239675669432</v>
+        <v>47.0625663335224</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.00480238459367</v>
+        <v>18.12789094380475</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.128383580968058</v>
+        <v>1.507105558112309</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0215521686955441</v>
+        <v>0.0776621789650937</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1531</v>
+        <v>1447</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>224.6175339338073</v>
+        <v>381.6144018708986</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>11.6</v>
+        <v>6.45</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.16166201037578</v>
+        <v>45.1485024231235</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.69739511189279</v>
+        <v>25.2522691364523</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1867802688723737</v>
+        <v>1.072867636151975</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.042185710400107</v>
+        <v>0.0134402701047384</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1464</v>
+        <v>1316</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>222.5704492150989</v>
+        <v>377.6321817322164</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>9.91</v>
+        <v>10.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.79177768180632</v>
+        <v>45.98283331848771</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>23.6046067726202</v>
+        <v>16.24815118381824</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6141546670778475</v>
+        <v>0.7526695038869646</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0073366327490004</v>
+        <v>0.0027043735380394</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1108</v>
+        <v>1231</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>217.0574406213609</v>
+        <v>375.3938416419151</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>11.05</v>
+        <v>76</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>35.57356666565728</v>
+        <v>26.94807876969452</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>36.98907361189854</v>
+        <v>28.19883449859764</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.380261820294185</v>
+        <v>1.246451296204247</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.025973930980943</v>
+        <v>-0.1689448335706194</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1541</v>
+        <v>1442</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>213.4909676852952</v>
+        <v>371.2527330883111</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>20.35</v>
+        <v>26.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.09945418178438</v>
+        <v>36.95069668413525</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.75884352555801</v>
+        <v>30.51690301104473</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.466753917329334</v>
+        <v>0.2990637034167111</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1663491580379266</v>
+        <v>0.0188999132344425</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1227</v>
+        <v>1109</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>212.9938240747165</v>
+        <v>370.452268160796</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>28.1</v>
+        <v>13.05</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.06256624406539</v>
+        <v>34.10517833552899</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.12789093885967</v>
+        <v>37.64021490431598</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.507105558112309</v>
+        <v>1.030622623823407</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.07766217901316359</v>
+        <v>-0.008447590092534599</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1213</v>
+        <v>1531</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>212.5033987441284</v>
+        <v>364.6175339338074</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>26.01634455894033</v>
+        <v>45.16166201037578</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.2200208430535</v>
+        <v>16.69739512491627</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0</v>
+        <v>0.1867802688723737</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.4775762293897435</v>
+        <v>0.042185710400107</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1540</v>
+        <v>1215</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>207.7170325891032</v>
+        <v>363.3349884381967</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>18.5</v>
+        <v>106.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>28.59687111005029</v>
+        <v>48.99585431528936</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.77202872852211</v>
+        <v>15.41867496397314</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.9289298841609128</v>
+        <v>0.9682584726755786</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,11 +6188,11 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0463590367652579</v>
+        <v>0.2895636421778013</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>202.0762873291234</v>
+        <v>362.0762873291234</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>10.25</v>
@@ -6226,13 +6226,13 @@
         <v>40.44982670382254</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>22.65716758994212</v>
+        <v>22.65716747343176</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.443126613078874</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6245,27 +6245,27 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1341</v>
+        <v>1110</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>198.1596864529293</v>
+        <v>357.2208531292047</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>59.2</v>
+        <v>14.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>51.82257007919033</v>
+        <v>38.37299676542323</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7.716013972435606</v>
+        <v>42.72536458147307</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7251461988304093</v>
+        <v>0.2294035780294982</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>1.463406518405298</v>
+        <v>0.0444289235279252</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1218</v>
+        <v>1568</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>196.367211253446</v>
+        <v>350.1130268832524</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14.4</v>
+        <v>29.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.63109100289646</v>
+        <v>39.44270518717838</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7.220682132429285</v>
+        <v>21.17709541243132</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.435947637650796</v>
+        <v>0.9699421165124102</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0126213537977964</v>
+        <v>-0.3119739975219272</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1215</v>
+        <v>1540</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>193.3349884381949</v>
+        <v>347.7170325891031</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>106.5</v>
+        <v>18.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.99585424149864</v>
+        <v>28.59687120639809</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.41867497029569</v>
+        <v>11.7720287190114</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.9682584726755786</v>
+        <v>0.9289298841609128</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2895636420576146</v>
+        <v>-0.0463590368373627</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1582</v>
+        <v>1432</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>190.6670445232751</v>
+        <v>343.630815110612</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>70.3</v>
+        <v>14.95</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.68358355996457</v>
+        <v>41.80849543163861</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.4138624544768</v>
+        <v>17.79542632359958</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.783017366351463</v>
+        <v>1.327737519863379</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0312405592073204</v>
+        <v>0.0024047759005692</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1532</v>
+        <v>1454</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>190.1793555867957</v>
+        <v>342.0336709326682</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>21.7</v>
+        <v>12.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.97867441838422</v>
+        <v>51.61737050712036</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>21.87388514607741</v>
+        <v>25.28709461613063</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6240940712414285</v>
+        <v>1.036776325956798</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.00791329703596</v>
+        <v>0.0470080613812416</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1423</v>
+        <v>1218</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>187.9461568905452</v>
+        <v>336.367211253446</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>34</v>
+        <v>14.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.09064197259551</v>
+        <v>47.63109109371245</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>9.443981123486024</v>
+        <v>7.220682181283551</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.351261240022901</v>
+        <v>1.435947637650796</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1122981808615031</v>
+        <v>0.0126213537377117</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1110</v>
+        <v>1417</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>187.2208531292047</v>
+        <v>334.9015094052575</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.3729966900639</v>
+        <v>46.67880233597773</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>42.72536444747984</v>
+        <v>14.49456900930805</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2294035780294982</v>
+        <v>1.0249939378989</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0444289235880134</v>
+        <v>0.0094612609138053</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1529</v>
+        <v>1582</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>186.3461820892714</v>
+        <v>330.6670445232754</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14.65</v>
+        <v>70.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>33.91078622023083</v>
+        <v>44.68358366323607</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.60013510258792</v>
+        <v>13.41386247000872</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6288506569291956</v>
+        <v>0.783017366351463</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0324710390764975</v>
+        <v>0.0312405592313504</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1201</v>
+        <v>1423</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>184.9739524337296</v>
+        <v>327.9461568905452</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.55</v>
+        <v>34</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.44706938610919</v>
+        <v>51.09064197026976</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>42.16239474527433</v>
+        <v>9.443981125092767</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7005999911207049</v>
+        <v>0.351261240022901</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0255818482225152</v>
+        <v>-0.1122981808134321</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1471</v>
+        <v>1201</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>179.4855376863688</v>
+        <v>324.9739524337295</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>9.06</v>
+        <v>11.55</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>34.09341164581301</v>
+        <v>43.44706928066739</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.87957553541817</v>
+        <v>42.16239462299019</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3234920981488099</v>
+        <v>0.7005999911207049</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0229791062865073</v>
+        <v>0.0255818482345333</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>177.0954423287757</v>
+        <v>324.5563887239823</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.4884048117181</v>
+        <v>39.65732332951707</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.98579582029763</v>
+        <v>13.9395788808684</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.9550313923867584</v>
+        <v>0.6355367549608758</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.002782556293289</v>
+        <v>-0.0254322728619643</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1203</v>
+        <v>1519</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>174.6887457232979</v>
+        <v>322.7134485326376</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>43.3</v>
+        <v>644</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>48.09810659614772</v>
+        <v>38.30781523038006</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8.282499238533783</v>
+        <v>12.1835773147189</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7134200073207435</v>
+        <v>0.7901326335294454</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0618276437458267</v>
+        <v>-4.909331117570293</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1104</v>
+        <v>1471</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>167.5509057137478</v>
+        <v>319.4855376863688</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>26.85</v>
+        <v>9.06</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.43445227326318</v>
+        <v>34.09341169618801</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.69509860253785</v>
+        <v>13.87957555466928</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.8808516881669476</v>
+        <v>0.3234920981488099</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0350572587288507</v>
+        <v>-0.0229791062865073</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1446</v>
+        <v>1217</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>153.1209022280734</v>
+        <v>317.0954423287757</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>13.45</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.68895823281994</v>
+        <v>42.48840512104703</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.27500246622376</v>
+        <v>15.98579579133908</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5468840712643926</v>
+        <v>0.9550313923867584</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0196980249657617</v>
+        <v>-0.0027825563173232</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1525</v>
+        <v>1104</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>133.1905600840464</v>
+        <v>307.5509057137478</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>62.8</v>
+        <v>26.85</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.35016851369349</v>
+        <v>49.43445205884161</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9.26565344584685</v>
+        <v>17.69509862667582</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5403780714278046</v>
+        <v>0.8808516881669476</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.367921627905277</v>
+        <v>0.0350572587889394</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1468</v>
+        <v>1435</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>128.5325403139668</v>
+        <v>304.5431623454882</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>13.2</v>
+        <v>20.15</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>49.27045516688506</v>
+        <v>49.94075312845314</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>8.179543341605802</v>
+        <v>6.890171799078288</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.588154802343977</v>
+        <v>1.583195300589184</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,11 +7089,11 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0039522323648479</v>
+        <v>0.1349177961683211</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>126.3659997319094</v>
+        <v>266.3659997319099</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>21.6</v>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.647744837994</v>
+        <v>47.64774481555023</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7.130574928608914</v>
+        <v>7.130574949934834</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.331162348368983</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,11 +7142,11 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0326654510096124</v>
+        <v>0.0326654509855803</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>113.5696243312159</v>
+        <v>253.5696243312159</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>25.5</v>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>39.74045088524456</v>
+        <v>39.74045104535397</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.08061956507233</v>
+        <v>18.08061958476425</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.9562453542493132</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0389250644700745</v>
+        <v>-0.0389250646022626</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>104.4184321255658</v>
+        <v>243.7148834084768</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>28.85</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>28.48470548548934</v>
+        <v>38.74514950811741</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>13.409113392563</v>
+        <v>16.12221857400366</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.105364653623886</v>
+        <v>0.0130458585223235</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.08514472338044091</v>
+        <v>-0.6609080684608657</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1536</v>
+        <v>1530</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>104.1625361635956</v>
+        <v>233.4498503776814</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>44.15</v>
+        <v>26.55</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>30.58555114335236</v>
+        <v>42.86116933168848</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>18.09283342385841</v>
+        <v>20.69120788820917</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.9111332174066584</v>
+        <v>0.5864870653200853</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1221192788933291</v>
+        <v>0.0703550669036033</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1432</v>
+        <v>1533</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>93.63081511061372</v>
+        <v>219.4184321255662</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>14.95</v>
+        <v>28.85</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>41.80849483100779</v>
+        <v>28.48470530469677</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>17.79542632359958</v>
+        <v>13.40911338894792</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.327737519863379</v>
+        <v>1.105364653623886</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.002404775924603</v>
+        <v>-0.0851447232722824</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1417</v>
+        <v>1536</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>84.90150940525753</v>
+        <v>219.1625361635948</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>44.15</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46.6788017105909</v>
+        <v>30.58555064706616</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>14.49456913003235</v>
+        <v>18.09283347292715</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.0249939378989</v>
+        <v>0.9111332174066584</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.0094612609162087</v>
+        <v>-0.1221192783164994</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1435</v>
+        <v>1213</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>84.54316234548826</v>
+        <v>212.5033987441284</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>20.15</v>
+        <v>0</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>49.94075360519775</v>
+        <v>26.01634456744229</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>6.890171993320638</v>
+        <v>10.22002084305351</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.583195300589184</v>
+        <v>0</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1349177908379224</v>
+        <v>-0.4775762293777264</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1219</v>
+        <v>1529</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>74.55638872398228</v>
+        <v>186.3461820892715</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>11.1</v>
+        <v>14.65</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>39.65732329468801</v>
+        <v>33.91078615447974</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>13.93957881199099</v>
+        <v>19.60013507905296</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.6355367549608758</v>
+        <v>0.6288506569291956</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,11 +7513,11 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0254322728379302</v>
+        <v>-0.0324710390885132</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
